--- a/output/OR202605280844126040_price_match.xlsx
+++ b/output/OR202605280844126040_price_match.xlsx
@@ -73,12 +73,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EA"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202605280844126040  ·  Date: 05/28/2026  ·  Patient: McGraw Jr, Robert Paul  ·  Generated: 2026-06-25 07:20</t>
+          <t>Henry Schein Price Match Negotiation  ·  Ref: OR202605280844126040  ·  Date: 05/28/2026  ·  Patient: McGraw Jr, Robert Paul  ·  Generated: 2026-06-25 22:54</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -676,41 +676,41 @@
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>3120199</t>
+          <t>3333466</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>425003</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk</t>
+          <t>Fuji II LC Capsules A3 48/Bx</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>518.89</v>
+        <v>372.66</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>360.1</v>
+        <v>312.41</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>POSSIBLE (65%)</t>
+          <t>EXACT (99%)</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>net32.com</t>
+          <t>carolinadental.com</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/genie-magic-mix-vps-impression-material-heavy-d-172999</t>
+          <t>https://carolinadental.com/products/fuji-ii-lc-capsules-a3-48-bx</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Matching: product name, form/spec, pack size · Not matching: brand · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Brand mismatch (Sultan vs Henry Schein). Product name mismatch (Rapid Set Berry Flavor, Purple vs Stand Bulk).</t>
+          <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
-        <v>158.79</v>
+        <v>60.25</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>317.58</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
@@ -741,21 +741,21 @@
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
       <c r="F5" s="12" t="n">
-        <v>199.99</v>
+        <v>319.32</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>UNVERIFIED PRICE (98%)</t>
+          <t>EXACT (80%)</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>alpinedentalshop.com</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>https://alpinedentalshop.com/products/genie-vps-heavy-body-4-x-380ml-cartridge?variant=51608080941370&amp;country=US&amp;currency=USD</t>
+          <t>https://www.supplyclinic.com/items/fuji-ii-lc-capsules-a3-48-bx-gc-america-425003?kw=&amp;cpn=23795785166</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
@@ -765,14 +765,14 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>⚠ PRICE UNRELIABLE — auto-extracted price conflicts with the listing; confirm on the page before using · Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
         </is>
       </c>
       <c r="L5" s="12" t="n">
-        <v>318.9</v>
+        <v>53.34</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>637.8</v>
+        <v>106.68</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
@@ -786,78 +786,78 @@
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="12" t="n">
-        <v>500.43</v>
+        <v>208.83</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (0%)</t>
+          <t>APPROXIMATE (77%)</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>supplyclinic.com</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/genie-vps-rapid-set-heavy-body-magic-mix-bulk-kit-380ml-4-box-sultan-healthcare-78830</t>
+          <t>https://www.net32.com/ec/gc-fuji-ii-lc-a3-capsules-50-d-20149</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50-pack price (ordered pack: 48)</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page ? vs ordered 4) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Not matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · No product information or pricing found on the page.</t>
+          <t>PACK MISMATCH (page 50 vs ordered 48) · Matching: brand, product name, form/spec · Not matching: pack size · price set from net32.com seller table: lowest available (incl. shipping) of 10 seller(s), via Lowest Price row · Pack quantity mismatch (ordered 48, page sells 50). No pricing information found on the page. · PACK MISMATCH — page is 50/pack but ordered 48/pack; treated as approximate, VERIFY</t>
         </is>
       </c>
       <c r="L6" s="12" t="n">
-        <v>18.46</v>
+        <v>163.83</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>36.92</v>
+        <v>327.66</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>3120199</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>7210FF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>278.99</v>
+        <v>518.89</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>233.81</v>
+        <v>360.1</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>EXACT (64%)</t>
+          <t>POSSIBLE (65%)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>supplyclinic.com</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/clinpro-clear-fluoride-treatment-0-5ml-100-pk-flavorless-3m-7210ff</t>
+          <t>https://www.net32.com/ec/genie-magic-mix-vps-impression-material-heavy-d-172999</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -867,14 +867,14 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed</t>
+          <t>Matching: product name, form/spec, pack size · Not matching: brand · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Brand mismatch (Sultan vs Henry Schein). Product name mismatch (Rapid Set Berry Flavor, Purple vs Stand Bulk).</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
-        <v>45.18</v>
+        <v>158.79</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>225.9</v>
+        <v>317.58</v>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
@@ -888,26 +888,26 @@
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10" t="inlineStr"/>
       <c r="F8" s="12" t="n">
-        <v>241</v>
+        <v>495.95</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>EXACT (99%)</t>
+          <t>EXACT (98%)</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>crazydentalprices.com</t>
+          <t>alpinedentalshop.com</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Clinpro-Clear-Fluoride-Treatment-0.5mL-100-Pk-Flavorless</t>
+          <t>https://alpinedentalshop.com/products/genie-vps-heavy-body-4-x-380ml-cartridge?variant=51608080941370&amp;country=US&amp;currency=USD</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>Buy 4 Get 1 Free! (Manufacturer Fulfilled)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
@@ -916,112 +916,112 @@
         </is>
       </c>
       <c r="L8" s="12" t="n">
-        <v>37.99</v>
+        <v>22.94</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>189.95</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>3120114</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>21521</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ReSURGE Inst Cleaning Solution 33oz/Bt</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>91.15000000000001</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>66.29000000000001</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>newarkdentalpemco.com</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>https://newarkdentalpemco.com/products/resurge-inst-cleaning-solution</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="12" t="n">
+        <v>500.43</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>supplyclinic.com</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/genie-vps-rapid-set-heavy-body-magic-mix-bulk-kit-380ml-4-box-sultan-healthcare-78830</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered 4) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Not matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · No product information or pricing found on the page.</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>36.92</v>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7772551</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>7210FF</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>278.99</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>233.81</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (64%)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>supplyclinic.com</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/clinpro-clear-fluoride-treatment-0-5ml-100-pk-flavorless-3m-7210ff</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
-      <c r="L9" s="7" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>149.16</v>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="12" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (98%)</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>thedentalmarket.net</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>https://thedentalmarket.net/featured-items/resurge-instrument-cleaning-solution-1l-33-8-oz-makes-67-gallons-unique/</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>on sale: was $95.95, now $76.95 (20% off)</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>85.2</v>
+      <c r="L10" s="7" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>225.9</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
@@ -1029,44 +1029,44 @@
       <c r="B11" s="10" t="inlineStr"/>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="12" t="n">
-        <v>63.99</v>
+        <v>241</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (54%)</t>
+          <t>EXACT (99%)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>safcodental.com</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/resurge-trade</t>
+          <t>https://www.crazydentalprices.com/Clinpro-Clear-Fluoride-Treatment-0.5mL-100-Pk-Flavorless</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4 Get 1 Free! (Manufacturer Fulfilled)</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: brand, product name · Not matching: form/spec, pack size · Page lists 'From $63.99' but does not specify the size or pack quantity for this price. Cannot confirm size/form or pack match.</t>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
         </is>
       </c>
       <c r="L11" s="12" t="n">
-        <v>27.16</v>
+        <v>37.99</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>162.96</v>
+        <v>189.95</v>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
@@ -1127,321 +1127,309 @@
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="12" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>UNVERIFIED PRICE (35%)</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>frontierdental.com</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.frontierdental.com/us/fr/product/mixing-tips-for-50-ml-cartridges-teal-48-pk-77586</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>⚠ PRICE UNRELIABLE — auto-extracted price conflicts with the listing; confirm on the page before using · PACK MISMATCH (page ? vs ordered 48) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: product name · Not matching: brand, form/spec, pack size · PRICE UNVERIFIED — no price could be read off the product page; value shown is from the search listing only, VERIFY MANUALLY · No price found on the page. Brand is not specified, but the ordered brand is DMG.</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>205.92</v>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3120114</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>21521</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ReSURGE Inst Cleaning Solution 33oz/Bt</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>thedentalmarket.net</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/featured-items/resurge-instrument-cleaning-solution-1l-33-8-oz-makes-67-gallons-unique/</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>on sale: was $95.95, now $76.95 (20% off)</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="12" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (54%)</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>safcodental.com</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.safcodental.com/product/resurge-trade</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: brand, product name · Not matching: form/spec, pack size · Page lists 'From $63.99' but does not specify the size or pack quantity for this price. Cannot confirm size/form or pack match.</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>162.96</v>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>3122330</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>0077650FG</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>121.6</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>103.95</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>APPROXIMATE (66%)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>dentalwholesaledirect.com</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>https://dentalwholesaledirect.com/impression-materials/genie-impression-material-putty-rapid-set-600-ml-pk/</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>on sale: was $124.95, now $103.95 (17% off)</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: product name, pack size · Not matching: brand, form/spec · Brand mismatch (Dentsply Sirona vs Henry Schein). Size mismatch (2x300ml jars = 600ml vs 2x445 Gr).</t>
         </is>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L16" s="7" t="n">
         <v>17.65</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M16" s="9" t="n">
         <v>52.95</v>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="12" t="n">
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="12" t="n">
         <v>70.95</v>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (49%)</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>thedentalmarket.net</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>https://thedentalmarket.net/dental-supplies/genie-putty-rapid-set/</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>on sale: was $88.95, now $70.95 (20% off)</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: product name · Not matching: brand, form/spec, pack size · Brand mismatch (Sultan vs Henry Schein). Pack quantity and size/form not specified on page.</t>
         </is>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>50.65</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>151.95</v>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>3333466</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>425003</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Fuji II LC Capsules A3 48/Bx</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>3333468</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>425004</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A3.5 48/Bx</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>372.66</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>312.41</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>EXACT (99%)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>carolinadental.com</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>https://carolinadental.com/products/fuji-ii-lc-capsules-a3-48-bx</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="F18" s="7" t="n">
+        <v>330.94</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (64%)</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>supplyclinic.com</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/fuji-ii-lc-capsules-a3-5-48-bx-gc-america-425004</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
-      <c r="L15" s="7" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>120.5</v>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>1126830</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>5703541</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (73%)</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>afteractionmedical.com</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>https://afteractionmedical.com/shop/criterion-n300-ultra-nitrile-exam-gloves/</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Purchases of $200 or more will receive free shipping at checkout. (UPS Ground service only. Valid in Continental United States only.)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page 300 vs ordered 300) · VARIANT MISMATCH (ordered: Ice Blue Small) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $14.99 (page SKU 1126830 == order MPN 5703541) · Price range is shown, but no specific price for the 'Ice Blue, Small (300 per Box)' variant is displayed without selecting it. The page lists the ordered MPN 570-3541 as a Henry Schein number, but does not explicitly state it is the MPN for the 'Ice Blue, Small (300 per Box)' variant. The page also lists 'Ice Blue, X-Large (250 per Box)' and 'Electric Blue, X-Large (250 per Box)' as 250 count, while other variants are 300 count. Without selecting the specific variant, a precise price cannot be extracted.</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>92.8</v>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>8969286</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>8969286</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT (81%)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>dentalwholesaledirect.com</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>https://dentalwholesaledirect.com/disposables/cotton-rolls-non-sterile-2-2000-bx/</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>on sale: was $26.95, now $21.95 (19% off)</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>47.4</v>
-      </c>
-    </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (99%)</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>fireflysupply.com</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>https://www.fireflysupply.com/products/henry-schein-size-2-medium-premium-cotton-rolls-1-5-length-0-375-diameter-2000-box-non-sterile-white-latex-free-ideal-for-dental-and-medical-use?variant=49006093893884</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>21.2</v>
+      <c r="L18" s="7" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>83.44</v>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
@@ -1449,158 +1437,146 @@
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="10" t="inlineStr"/>
       <c r="F19" s="12" t="n">
-        <v>14.99</v>
+        <v>355.62</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (64%)</t>
+          <t>EXACT (64%)</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>dentalcity.com</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/2223/dental-city-2-medium-cotton-rolls-2000box</t>
+          <t>https://www.net32.com/ec/gc-fuji-ii-lc-a35-capsules-48-d-130428</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>on sale: was $22.99, now $14.99 (35% off)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>VARIANT MISMATCH (ordered: #2 Non-Sterile) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Dental City vs Henry Schein). Product name is 'Medium Cotton Rolls' instead of 'Premium Cotton Rolls'.</t>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
         </is>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18.81</v>
+        <v>17.04</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>75.23999999999999</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>3250498</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>80779741</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>44.99</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="12" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>EXACT (99%)</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-84837276</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Fuji-II-LC-Capsules-425004_2</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>Quantity discounts available</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>60</v>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>33.68</v>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>8889527</t>
+          <t>8969286</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>PF1715</t>
+          <t>8969286</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk</t>
+          <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>71.7</v>
+        <v>33.8</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>42.31</v>
+        <v>21.95</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>EXACT (99%)</t>
+          <t>GENERIC EQUIVALENT (81%)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>usdentaldepot.com</t>
+          <t>dentalwholesaledirect.com</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/parapost-fiber-lux-posts-size-5-coltene-whaladent-pf1715</t>
+          <t>https://dentalwholesaledirect.com/disposables/cotton-rolls-non-sterile-2-2000-bx/</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Minimum quantity is 1.</t>
+          <t>on sale: was $26.95, now $21.95 (19% off)</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed</t>
+          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
-        <v>29.39</v>
+        <v>11.85</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>58.78</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
@@ -1614,21 +1590,21 @@
       <c r="D22" s="10" t="inlineStr"/>
       <c r="E22" s="10" t="inlineStr"/>
       <c r="F22" s="12" t="n">
-        <v>71.64</v>
+        <v>28.5</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (19%)</t>
+          <t>EXACT (99%)</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>supplyclinic.com</t>
+          <t>fireflysupply.com</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/parapost-fiber-lux-refill-size-5-5-pack-coltene-whaledent-pf1715</t>
+          <t>https://www.fireflysupply.com/products/henry-schein-size-2-medium-premium-cotton-rolls-1-5-length-0-375-diameter-2000-box-non-sterile-white-latex-free-ideal-for-dental-and-medical-use?variant=49006093893884</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -1638,128 +1614,116 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page ? vs ordered 5) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Red) · Matching: product name · Not matching: brand, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 4 seller(s), via min of Total column · No pricing information available on the page.</t>
+          <t>Exact — all four trust criteria confirmed (alternate source, higher price than Option 1)</t>
         </is>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0.06</v>
+        <v>5.3</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.12</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>1126831</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>1126831</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="F23" s="17" t="n">
+      <c r="A23" s="10" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="12" t="n">
         <v>14.99</v>
       </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (77%)</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="inlineStr">
-        <is>
-          <t>afteractionmedical.com</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>https://afteractionmedical.com/shop/criterion-n300-ultra-nitrile-exam-gloves/</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page 300 vs ordered 300) · VARIANT MISMATCH (ordered: Ice Blue Medium) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $14.99 (page SKU 1126831 == order MPN 1126831) · Price range shown, but no specific price for the ordered variant and pack quantity is displayed without selecting an option. The page lists 'Ice Blue, Medium (300 per Box)' which matches the order, but the price is not visible until selected.</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>58</v>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (64%)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>dentalcity.com</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/2223/dental-city-2-medium-cotton-rolls-2000box</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>on sale: was $22.99, now $14.99 (35% off)</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: #2 Non-Sterile) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Dental City vs Henry Schein). Product name is 'Medium Cotton Rolls' instead of 'Premium Cotton Rolls'.</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>7013349</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>DCA06-170-HP-BL/O</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>3250498</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>80779741</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (99%)</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-84837276</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Quantity discounts available</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>EXACT (88%)</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>net32.com</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/meisinger-hp-dca06170-prepolish-wheel-shaped-polisher-d-189729</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>11.46</v>
+      <c r="M24" s="9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="56" customHeight="1">
@@ -1773,242 +1737,242 @@
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="12" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>UNVERIFIED PRICE (4%)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>ddsdentalsupplies.com</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/floss-5/</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>⚠ PRICE UNRELIABLE — auto-extracted price conflicts with the listing; confirm on the page before using · PACK MISMATCH (page ? vs ordered 72) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Mint) · Not matching: brand, product name, form/spec, pack size · PRICE UNVERIFIED — no price could be read off the product page; value shown is from the search listing only, VERIFY MANUALLY · The page is a category page for 'Floss' and does not display a specific product or its price.</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>8889527</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>PF1715</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>EXACT (99%)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>usdentaldepot.com</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/parapost-fiber-lux-posts-size-5-coltene-whaladent-pf1715</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Minimum quantity is 1.</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>58.78</v>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="10" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="12" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (19%)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>supplyclinic.com</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/parapost-fiber-lux-refill-size-5-5-pack-coltene-whaledent-pf1715</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered 5) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Red) · Matching: product name · Not matching: brand, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 4 seller(s), via min of Total column · No pricing information available on the page.</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>7013349</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>DCA06-170-HP-BL/O</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (88%)</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>net32.com</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/meisinger-hp-dca06170-prepolish-wheel-shaped-polisher-d-189729</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>11.46</v>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="10" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
         <v>48.99</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>EXACT · VARIANT UNVERIFIED (73%)</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>safcodental.com</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/product/luster-zirconia-polishers</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="K29" s="14" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed · VARIANT UNVERIFIED — page did not confirm the ordered variant (Medium Blue/Orange); verify before buying (alternate source, higher price than Option 1)</t>
         </is>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>3.87</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>23.22</v>
-      </c>
-    </row>
-    <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="10" t="inlineStr"/>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="12" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (23%)</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/zirconia-polisher-blue-orange-smoothing-wheel-11-0mm-hp-2-pk-meisinger-usa-dca05-110-hp-bl-o</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: product name · Not matching: brand, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 2 seller(s), via min of Total column · No pricing information found on the page. MPN DCA05-110-HP-BL/O does not match ordered DCA06-170-HP-BL/O.</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>57.78</v>
-      </c>
-    </row>
-    <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>3120212</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>0077600FG</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>36.69</v>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>EXACT (84%)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/genie-vps-standard-set-extra-light-body-50ml-2-pack-sultan-healthcare-77605</t>
-        </is>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
-        <is>
-          <t>Exact — all four trust criteria confirmed</t>
-        </is>
-      </c>
-      <c r="L27" s="23" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M27" s="25" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="10" t="inlineStr"/>
-      <c r="B28" s="10" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="12" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (77%)</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>thedentalmarket.net</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>https://thedentalmarket.net/dental-supplies/genie-2-x-50ml-cartridges-tips-berry-flavour-light-body-standard-set/</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>on sale: was $33.95, now $26.95 (21% off)</t>
-        </is>
-      </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: XLight Body) · Matching: brand, form/spec, pack size · Not matching: product name · Variant 'Berry Flavor, Light Body Standard Set' does not exactly match 'XLight Body'.</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>49.25</v>
-      </c>
-    </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>3865728</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>002039605</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Speedclean For Autoclave 16oz/Bt</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>POSSIBLE (39%)</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>skydentalsupply.com</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/autoclave-cleaner--quart--00146.htm</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>Minimal quantity for this product is 1</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Matching: pack size · Not matching: brand, product name, form/spec · Brand 'EPR Industries, LLC' does not match 'Henry Schein'. Product name 'Autoclave Cleaning Solution' does not match 'Speedclean For Autoclave'. Size/form '1QT bottle (32 FL.oz)' does not match '16oz/Bt'.</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="30" ht="56" customHeight="1">
@@ -2016,27 +1980,27 @@
       <c r="B30" s="10" t="inlineStr"/>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
+          <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
       <c r="E30" s="10" t="inlineStr"/>
       <c r="F30" s="12" t="n">
-        <v>26.68</v>
+        <v>43.23</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (62%)</t>
+          <t>POSSIBLE (23%)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>dentalcity.com</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/9003/midmark-speedclean-autoclave-cleaner-16oz</t>
+          <t>https://www.supplyclinic.com/items/zirconia-polisher-blue-orange-smoothing-wheel-11-0mm-hp-2-pk-meisinger-usa-dca05-110-hp-bl-o</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -2046,42 +2010,54 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>VARIANT MISMATCH (ordered: specified) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Midmark vs SciCan) and MPN mismatch (MID002039600 vs 002039605).</t>
+          <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · Matching: product name · Not matching: brand, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 2 seller(s), via min of Total column · No pricing information found on the page. MPN DCA05-110-HP-BL/O does not match ordered DCA06-170-HP-BL/O.</t>
         </is>
       </c>
       <c r="L30" s="12" t="n">
-        <v>9.31</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>18.62</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="10" t="inlineStr"/>
-      <c r="B31" s="10" t="inlineStr"/>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="10" t="inlineStr"/>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>3120212</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>0077600FG</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>36.8</v>
+      </c>
       <c r="F31" s="12" t="n">
-        <v>16.92</v>
+        <v>36.69</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (58%)</t>
+          <t>EXACT (84%)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>ciamedical.com</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>https://www.ciamedical.com/midmark-002039600-each-speedclean-for-autoclave-16oz-bt-12-ea-cs</t>
+          <t>https://www.supplyclinic.com/items/genie-vps-standard-set-extra-light-body-50ml-2-pack-sultan-healthcare-77605</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
@@ -2091,116 +2067,116 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 1 vs ordered ?) · Matching: product name, form/spec · Not matching: brand, pack size · Brand 'Midmark' does not match 'Henry Schein'. MPN '002039600' does not match '002039605'. The page sells a single 16oz bottle, but the title indicates '12 EA/CS' which is a case quantity, leading to ambiguity. Assuming 'Sell Unit: EACH' refers to a single 16oz bottle. The ordered pack quantity is 'None', but the page sells a single unit from a 12-pack case.</t>
+          <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
       <c r="L31" s="12" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>38.14</v>
+        <v>0.11</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="32" ht="56" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>2222660</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>CW-6162</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>62.75</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>APPROXIMATE (50%)</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/dynamic-mixing-tip-yellow-40-pack-coltene-whaledent-6162</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec, pack size · Not matching: brand, product name · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · Price requires login. Brand mismatch (Kulzer vs Coltene Whaledent). Product name mismatch. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>13.85</v>
+      <c r="A32" s="10" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="12" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>thedentalmarket.net</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/dental-supplies/genie-2-x-50ml-cartridges-tips-berry-flavour-light-body-standard-set/</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>on sale: was $33.95, now $26.95 (21% off)</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: XLight Body) · Matching: brand, form/spec, pack size · Not matching: product name · Variant 'Berry Flavor, Light Body Standard Set' does not exactly match 'XLight Body'.</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>49.25</v>
       </c>
     </row>
     <row r="33" ht="56" customHeight="1">
-      <c r="A33" s="10" t="inlineStr"/>
-      <c r="B33" s="10" t="inlineStr"/>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="12" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (43%)</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>ansondental.com</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>https://ansondental.com/products/premium-dental-dynamic-mixing-tips-yellow-including-ring?currency=USD&amp;country=US&amp;variant=30916149313670&amp;stkn=84caddec0854&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec · Not matching: brand, product name, pack size · Brand is Anson Dental, not Kulzer. Pack quantity is 50, not 40. Product description mentions compatibility with Kulzer, but it's not a Kulzer branded product.</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>36.61</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>3865728</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>002039605</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Speedclean For Autoclave 16oz/Bt</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>POSSIBLE (39%)</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/autoclave-cleaner--quart--00146.htm</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Minimal quantity for this product is 1</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified) · Matching: pack size · Not matching: brand, product name, form/spec · Brand 'EPR Industries, LLC' does not match 'Henry Schein'. Product name 'Autoclave Cleaning Solution' does not match 'Speedclean For Autoclave'. Size/form '1QT bottle (32 FL.oz)' does not match '16oz/Bt'.</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="34" ht="56" customHeight="1">
@@ -2208,203 +2184,191 @@
       <c r="B34" s="10" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
+          <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="12" t="n">
-        <v>59.99</v>
+        <v>26.68</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>APPROXIMATE (35%)</t>
+          <t>POSSIBLE (62%)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>net32.com</t>
+          <t>dentalcity.com</t>
         </is>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/kerr-dynamic-yellow-mixing-tips-380-ml-d-177998</t>
+          <t>https://dentalcity.com/product/9003/midmark-speedclean-autoclave-cleaner-16oz</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>50-pack price (ordered pack: 40)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec · Not matching: brand, product name, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 8 seller(s), via Lowest Price row · Price requires login. Brand mismatch (Kulzer vs Kerr). Pack quantity mismatch (40 vs 50). Product name mismatch. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total · PACK MISMATCH — page is 50/pack but ordered 40/pack; treated as approximate, VERIFY</t>
+          <t>VARIANT MISMATCH (ordered: specified) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Midmark vs SciCan) and MPN mismatch (MID002039600 vs 002039605).</t>
         </is>
       </c>
       <c r="L34" s="12" t="n">
-        <v>16.61</v>
+        <v>9.31</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>16.61</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>7013185</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>9742M-040-HP-BL/O</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Meisinger Polisher HP 9742M-040 2/Pk</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>47.55</v>
-      </c>
+      <c r="A35" s="10" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
       <c r="F35" s="12" t="n">
-        <v>45.49</v>
+        <v>16.92</v>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>EXACT (99%)</t>
+          <t>POSSIBLE (58%)</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>crazydentalprices.com</t>
+          <t>ciamedical.com</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Meisinger-Polishers-9742M-040-HP-BL-O</t>
+          <t>https://www.ciamedical.com/midmark-002039600-each-speedclean-for-autoclave-16oz-bt-12-ea-cs</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>Buy 4 Get 1 Free! (Manufacturer Fulfilled)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Exact — all four trust criteria confirmed</t>
+          <t>PACK MISMATCH (page 1 vs ordered ?) · Matching: product name, form/spec · Not matching: brand, pack size · Brand 'Midmark' does not match 'Henry Schein'. MPN '002039600' does not match '002039605'. The page sells a single 16oz bottle, but the title indicates '12 EA/CS' which is a case quantity, leading to ambiguity. Assuming 'Sell Unit: EACH' refers to a single 16oz bottle. The ordered pack quantity is 'None', but the page sells a single unit from a 12-pack case.</t>
         </is>
       </c>
       <c r="L35" s="12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M35" s="20" t="n">
-        <v>12.36</v>
+        <v>19.07</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>38.14</v>
       </c>
     </row>
     <row r="36" ht="56" customHeight="1">
-      <c r="A36" s="10" t="inlineStr"/>
-      <c r="B36" s="10" t="inlineStr"/>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2222660</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>CW-6162</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (50%)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>supplyclinic.com</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/dynamic-mixing-tip-yellow-40-pack-coltene-whaledent-6162</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec, pack size · Not matching: brand, product name · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · Price requires login. Brand mismatch (Kulzer vs Coltene Whaledent). Product name mismatch. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>13.85</v>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="10" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   ↳ Option 2</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr"/>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="12" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (77%)</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>avtecdental.com</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>https://www.avtecdental.com/products/polisher-diamond-impregnated-for-porcelain-blue-orange-point-4mm-o-polishing-medium-hp-9742m-040-hp-bl-o</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="12" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (43%)</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>ansondental.com</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>https://ansondental.com/products/premium-dental-dynamic-mixing-tips-yellow-including-ring?currency=USD&amp;country=US&amp;variant=30916149313670&amp;stkn=84caddec0854&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page ? vs ordered 2) · Matching: brand, product name, form/spec · Not matching: pack size · MPN matches, but the ordered pack quantity is 2 and the page does not specify pack quantity, implying a single unit. Also, the ordered description 'Meisinger Polisher HP 9742M-040 2/Pk' implies a pack of 2, while the page sells a single unit.</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="37" ht="56" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>2013820</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>671131</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Mity K-Files 25mm #10 6/Pk</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>POSSIBLE (56%)</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>thedentalmarket.net</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>https://thedentalmarket.net/endodontic/nickel-titanium-reamer-files-25mm/?sku=DI-NT501-211</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>on sale: was $10.95, now $8.95 (18% off)</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand and product name mismatch. Ordered Dentsply Sirona Mity K-Files, page is Diadent Nickel Titanium Reamer Files.</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>32.9</v>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec · Not matching: brand, product name, pack size · Brand is Anson Dental, not Kulzer. Pack quantity is 50, not 40. Product description mentions compatibility with Kulzer, but it's not a Kulzer branded product.</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>36.61</v>
       </c>
     </row>
     <row r="38" ht="56" customHeight="1">
@@ -2412,203 +2376,203 @@
       <c r="B38" s="10" t="inlineStr"/>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ↳ Option 2</t>
+          <t xml:space="preserve">   ↳ Option 3</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr"/>
       <c r="E38" s="10" t="inlineStr"/>
       <c r="F38" s="12" t="n">
-        <v>11.49</v>
+        <v>59.99</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>POSSIBLE (64%)</t>
+          <t>APPROXIMATE (35%)</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>dentalcity.com</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/2284/dental-city-dental-k-files-25mm</t>
+          <t>https://www.net32.com/ec/kerr-dynamic-yellow-mixing-tips-380-ml-d-177998</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
+          <t>50-pack price (ordered pack: 40)</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock) · Matching: form/spec · Not matching: brand, product name, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 8 seller(s), via Lowest Price row · Price requires login. Brand mismatch (Kulzer vs Kerr). Pack quantity mismatch (40 vs 50). Product name mismatch. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total · PACK MISMATCH — page is 50/pack but ordered 40/pack; treated as approximate, VERIFY</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>7013185</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>9742M-040-HP-BL/O</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Meisinger Polisher HP 9742M-040 2/Pk</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>EXACT (99%)</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Meisinger-Polishers-9742M-040-HP-BL-O</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Buy 4 Get 1 Free! (Manufacturer Fulfilled)</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>Exact — all four trust criteria confirmed</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="10" t="inlineStr"/>
+      <c r="B40" s="10" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="12" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (77%)</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>avtecdental.com</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.avtecdental.com/products/polisher-diamond-impregnated-for-porcelain-blue-orange-point-4mm-o-polishing-medium-hp-9742m-040-hp-bl-o</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Dental City vs Dentsply Sirona) and product name mismatch (Dental K-Files vs Mity K-Files).</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>27.82</v>
-      </c>
-    </row>
-    <row r="39" ht="56" customHeight="1">
-      <c r="A39" s="10" t="inlineStr"/>
-      <c r="B39" s="10" t="inlineStr"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ↳ Option 3</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="12" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (62%)</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>skydentalsupply.com</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/k-file-size-25mm-premier.htm</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Premier vs Dentsply Sirona) and product name mismatch (K Files Premier vs Mity K-Files).</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>22.82</v>
-      </c>
-    </row>
-    <row r="40" ht="56" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>7011085</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>841G-012-FG</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Diamond FG Coarse 841G-012 5/Pk</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>43.65</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>UNVERIFIED PRICE (43%)</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>mrbur.com</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mrbur.com/products/cylinder-coarse-diamond-bur-fg-5pcs-pack</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>on sale: was $23.75, now $21.59 (9% off)</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>⚠ PRICE UNRELIABLE — auto-extracted price conflicts with the listing; confirm on the page before using · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: 841G-012) · Matching: pack size · Not matching: brand, product name, form/spec · The product is a 'Cylinder Coarse Diamond Bur FG' which is similar to 'Diamond FG Coarse'. The pack quantity matches (5pcs/pack). However, the ordered variant '841G-012' is not available, and the available variants are '15A', '15', '15B', '16', '80', '86A', '86', '86B'. The MPN '841G-012-FG' does not match any listed order numbers. The brand 'MR. BUR' is also different from the ordered 'None' (Henry Schein). · PRICE UNRELIABLE — $21.59 is far below the other sources for this item (median $53.95); likely a related-item or single-unit price, VERIFY MANUALLY</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>22.06</v>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered 2) · Matching: brand, product name, form/spec · Not matching: pack size · MPN matches, but the ordered pack quantity is 2 and the page does not specify pack quantity, implying a single unit. Also, the ordered description 'Meisinger Polisher HP 9742M-040 2/Pk' implies a pack of 2, while the page sells a single unit.</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>33.9</v>
       </c>
     </row>
     <row r="41" ht="56" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>1392761</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t>S3160K</t>
-        </is>
-      </c>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>S3+ Face Masks L3 Black 50/Bx</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="E41" s="23" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="F41" s="23" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="G41" s="21" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT (81%)</t>
-        </is>
-      </c>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>crazydentalprices.com</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>https://www.crazydentalprices.com/S3-S3160K</t>
-        </is>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="22" t="inlineStr">
-        <is>
-          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
-        </is>
-      </c>
-      <c r="L41" s="23" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M41" s="25" t="n">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2013820</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>671131</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Mity K-Files 25mm #10 6/Pk</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
         <v>2</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>POSSIBLE (56%)</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>thedentalmarket.net</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/endodontic/nickel-titanium-reamer-files-25mm/?sku=DI-NT501-211</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>on sale: was $10.95, now $8.95 (18% off)</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand and product name mismatch. Ordered Dentsply Sirona Mity K-Files, page is Diadent Nickel Titanium Reamer Files.</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>32.9</v>
       </c>
     </row>
     <row r="42" ht="56" customHeight="1">
@@ -2622,151 +2586,355 @@
       <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="10" t="inlineStr"/>
       <c r="F42" s="12" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (64%)</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>dentalcity.com</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>https://dentalcity.com/product/2284/dental-city-dental-k-files-25mm</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Dental City vs Dentsply Sirona) and product name mismatch (Dental K-Files vs Mity K-Files).</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>27.82</v>
+      </c>
+    </row>
+    <row r="43" ht="56" customHeight="1">
+      <c r="A43" s="10" t="inlineStr"/>
+      <c r="B43" s="10" t="inlineStr"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 3</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="12" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/k-file-size-25mm-premier.htm</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: #10 25mm) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Premier vs Dentsply Sirona) and product name mismatch (K Files Premier vs Mity K-Files).</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>22.82</v>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>7011085</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>841G-012-FG</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Diamond FG Coarse 841G-012 5/Pk</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>UNVERIFIED PRICE (43%)</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>mrbur.com</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mrbur.com/products/cylinder-coarse-diamond-bur-fg-5pcs-pack</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>on sale: was $23.75, now $21.59 (9% off)</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>⚠ PRICE UNRELIABLE — auto-extracted price conflicts with the listing; confirm on the page before using · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: 841G-012) · Matching: pack size · Not matching: brand, product name, form/spec · The product is a 'Cylinder Coarse Diamond Bur FG' which is similar to 'Diamond FG Coarse'. The pack quantity matches (5pcs/pack). However, the ordered variant '841G-012' is not available, and the available variants are '15A', '15', '15B', '16', '80', '86A', '86', '86B'. The MPN '841G-012-FG' does not match any listed order numbers. The brand 'MR. BUR' is also different from the ordered 'None' (Henry Schein). · PRICE UNRELIABLE — $21.59 is far below the other sources for this item (median $53.95); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>22.06</v>
+      </c>
+    </row>
+    <row r="45" ht="56" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>1392761</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>S3160K</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>S3+ Face Masks L3 Black 50/Bx</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT (81%)</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/S3-S3160K</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>GENERIC EQUIVALENT — same product type, different/no brand; no competitor sells the exact Schein house-brand item. Verify clinical equivalence before substituting.</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M45" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" ht="56" customHeight="1">
+      <c r="A46" s="10" t="inlineStr"/>
+      <c r="B46" s="10" t="inlineStr"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ↳ Option 2</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr"/>
+      <c r="E46" s="10" t="inlineStr"/>
+      <c r="F46" s="12" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (38%)</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="I42" s="13" t="inlineStr">
+      <c r="I46" s="13" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/cranberry-s3-earloop-masks-d-168843</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K42" s="14" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: L3 Black) · Matching: form/spec, pack size · Not matching: brand, product name · price set from net32.com seller table: lowest available (incl. shipping) of 10 seller(s), via Lowest Price row · Page is for Cranberry S3+ Earloop Masks, not Henry Schein S3+ Face Masks. No pricing information available.</t>
         </is>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>0.58</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>14.5</v>
       </c>
     </row>
-    <row r="43" ht="56" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="47" ht="56" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>9872474</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>305436</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D47" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="17" t="n">
+      <c r="E47" s="23" t="n">
         <v>17.42</v>
       </c>
-      <c r="F43" s="17" t="n">
+      <c r="F47" s="23" t="n">
         <v>16.17</v>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G47" s="21" t="inlineStr">
         <is>
           <t>EXACT (99%)</t>
         </is>
       </c>
-      <c r="H43" s="15" t="inlineStr">
+      <c r="H47" s="21" t="inlineStr">
         <is>
           <t>vitalitymedical.com</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I47" s="24" t="inlineStr">
         <is>
           <t>https://www.vitalitymedical.com/3-gallon-bd-patient-room-sharps-container-counter-balanced-lid-red-305436.html</t>
         </is>
       </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="J47" s="22" t="inlineStr">
         <is>
           <t>on sale: was $17.58, now $16.17 (8% off)</t>
         </is>
       </c>
-      <c r="K43" s="16" t="inlineStr">
+      <c r="K47" s="22" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L47" s="23" t="n">
         <v>1.25</v>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="M47" s="25" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="44" ht="56" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
+    <row r="48" ht="56" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>1024081</t>
         </is>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>1024081</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca</t>
         </is>
       </c>
-      <c r="D44" s="21" t="n">
+      <c r="D48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="23" t="n">
+      <c r="E48" s="12" t="n">
         <v>28.89</v>
       </c>
-      <c r="F44" s="23" t="n">
+      <c r="F48" s="12" t="n">
         <v>28.3</v>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>EXACT (80%)</t>
         </is>
       </c>
-      <c r="H44" s="21" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/tray-covers-ritter-b-aqua-8-5-x-12-25-1000-crosstex-fbaq</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr">
+      <c r="K48" s="14" t="inlineStr">
         <is>
           <t>Exact — all four trust criteria confirmed</t>
         </is>
       </c>
-      <c r="L44" s="23" t="n">
+      <c r="L48" s="12" t="n">
         <v>0.59</v>
       </c>
-      <c r="M44" s="25" t="n">
+      <c r="M48" s="20" t="n">
         <v>0.59</v>
       </c>
     </row>
@@ -2817,6 +2985,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
